--- a/tasks/AnalyticalCase/bin/output/WeeklyEffortPerProject.xlsx
+++ b/tasks/AnalyticalCase/bin/output/WeeklyEffortPerProject.xlsx
@@ -3415,7 +3415,7 @@
         <v>284</v>
       </c>
       <c r="B284" t="n" s="0">
-        <v>15.88</v>
+        <v>15.879999999999997</v>
       </c>
     </row>
     <row r="285">
